--- a/docs/Mapping_casi_uso/matrimoni/Sep_Div_007.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Sep_Div_007.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="178">
   <si>
     <t>Sezione</t>
   </si>
@@ -546,15 +546,6 @@
   </si>
   <si>
     <t>evento.intestatari[1]</t>
-  </si>
-  <si>
-    <t>Dettagli evento</t>
-  </si>
-  <si>
-    <t>Ricevuta da privato cittadino</t>
-  </si>
-  <si>
-    <t>ricevutaDaPrivatoCittadino</t>
   </si>
 </sst>
 </file>
@@ -613,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="20.62890625" customWidth="true" bestFit="true"/>
@@ -4466,29 +4457,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G168" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/Mapping_casi_uso/matrimoni/Sep_Div_007.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Sep_Div_007.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="183">
   <si>
     <t>Sezione</t>
   </si>
@@ -546,6 +546,21 @@
   </si>
   <si>
     <t>evento.intestatari[1]</t>
+  </si>
+  <si>
+    <t>Dettagli evento</t>
+  </si>
+  <si>
+    <t>Ricevuta da privato cittadino</t>
+  </si>
+  <si>
+    <t>ricevutaDaPrivatoCittadino</t>
+  </si>
+  <si>
+    <t>Tipo procedimento</t>
+  </si>
+  <si>
+    <t>tipoProcedimento</t>
   </si>
 </sst>
 </file>
@@ -604,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="20.62890625" customWidth="true" bestFit="true"/>
@@ -4457,6 +4472,52 @@
         <v>22</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
